--- a/boss_pack/readiness_scorecard.xlsx
+++ b/boss_pack/readiness_scorecard.xlsx
@@ -98,8 +98,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -137,12 +137,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t/>
+          <t>Interactive site</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>310 ranked public targets are available in the dashboard.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -154,12 +154,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t/>
+          <t>Live sale feed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t/>
+          <t>226 advertised sale listings are published; 226 came from the latest public refresh.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -171,12 +171,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t/>
+          <t>Sector taxonomy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t/>
+          <t>15 sectors and 104 subsectors are configured; 25 subsectors currently have observed targets/listings/evidence.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -188,12 +188,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t/>
+          <t>Approved source rows</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t/>
+          <t>33 of 120 approved source rows are complete (27.5%).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -205,12 +205,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t/>
+          <t>Company evidence gate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t/>
+          <t>Approved company-count evidence and source metadata are required before investment decisions.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
